--- a/Haunted-Mouse-FMOD/HauntedMouseSoundAssetList.xlsx
+++ b/Haunted-Mouse-FMOD/HauntedMouseSoundAssetList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lucash/Documents/GitHub/Design-Week-Fall-2025/Haunted-Mouse-FMOD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB2C181B-5C06-324B-A2D7-5B197A5FB9A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9FBE6C6-3E44-C04B-AC86-03168B511208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{641B9BD1-1F1D-1E4E-97CD-25C76D15BCBF}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="19">
   <si>
     <t>Name</t>
   </si>
@@ -62,7 +62,7 @@
     <t>monster_bite</t>
   </si>
   <si>
-    <t>No</t>
+    <t>Yes</t>
   </si>
   <si>
     <t>monster_taunt</t>
@@ -90,6 +90,9 @@
   </si>
   <si>
     <t>Ambient</t>
+  </si>
+  <si>
+    <t>Distance from mouse affects low EQ &amp; distortion</t>
   </si>
 </sst>
 </file>
@@ -125,13 +128,41 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="8">
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -145,16 +176,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F2081CC0-2DF5-5943-B30E-8C93F4AC4BF2}" name="Table2" displayName="Table2" ref="A1:G6" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F2081CC0-2DF5-5943-B30E-8C93F4AC4BF2}" name="Table2" displayName="Table2" ref="A1:G6" totalsRowShown="0" dataDxfId="0">
   <autoFilter ref="A1:G6" xr:uid="{F2081CC0-2DF5-5943-B30E-8C93F4AC4BF2}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{72342906-BAD8-0241-A656-E60FD08F48F1}" name="Name"/>
-    <tableColumn id="2" xr3:uid="{3B396E36-7F0E-3C48-9329-15D486CD5475}" name="Description"/>
-    <tableColumn id="3" xr3:uid="{F0193DE1-AFA7-7A41-A89B-5877825F4E01}" name="In FMOD"/>
-    <tableColumn id="4" xr3:uid="{7F81BC98-F3F8-4E42-8B63-130A8043250C}" name="In Unity"/>
-    <tableColumn id="5" xr3:uid="{4C1327BD-C340-9848-A1D1-A694B06CC653}" name="Notes"/>
-    <tableColumn id="6" xr3:uid="{CFAD1A83-3F13-6A4E-90C2-B8215D122DB1}" name="Parameters"/>
-    <tableColumn id="7" xr3:uid="{A0A198C0-6E94-0E43-A10D-2B84D58A49D4}" name="Category"/>
+    <tableColumn id="1" xr3:uid="{72342906-BAD8-0241-A656-E60FD08F48F1}" name="Name" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{3B396E36-7F0E-3C48-9329-15D486CD5475}" name="Description" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{F0193DE1-AFA7-7A41-A89B-5877825F4E01}" name="In FMOD" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{7F81BC98-F3F8-4E42-8B63-130A8043250C}" name="In Unity" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{4C1327BD-C340-9848-A1D1-A694B06CC653}" name="Notes" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{CFAD1A83-3F13-6A4E-90C2-B8215D122DB1}" name="Parameters" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{A0A198C0-6E94-0E43-A10D-2B84D58A49D4}" name="Category" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -509,73 +540,90 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:7" ht="68" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="B2" s="1"/>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="3" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="B3" s="1"/>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+    <row r="4" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="B4" s="1"/>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+    <row r="5" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="B5" s="1"/>
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+    <row r="6" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1" t="s">
         <v>17</v>
       </c>
     </row>
